--- a/data/list_players_register.xlsx
+++ b/data/list_players_register.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,6 +515,44 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Patrick Drewes</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Watch</t>
         </is>
       </c>
     </row>
